--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31ABA46-EC1F-4EE0-B4F1-B232223E364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AFA849-8C0D-4F01-BECC-A65CDF901227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -1361,643 +1361,643 @@
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>elc_wof_002</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity generation in cluster -- 2</t>
   </si>
   <si>
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity generation in cluster -- 3</t>
   </si>
   <si>
     <t>elc_wof_004</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity generation in cluster -- 4</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity generation in cluster -- 5</t>
   </si>
   <si>
     <t>elc_wof_006</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity generation in cluster -- 6</t>
   </si>
   <si>
     <t>elc_wof_007</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity generation in cluster -- 7</t>
   </si>
   <si>
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity generation in cluster -- 8</t>
   </si>
   <si>
     <t>elc_wof_009</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity generation in cluster -- 9</t>
   </si>
   <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity generation in cluster -- 10</t>
   </si>
   <si>
     <t>elc_wof_011</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 11</t>
+    <t>wind offshore electricity generation in cluster -- 11</t>
   </si>
   <si>
     <t>elc_wof_012</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 12</t>
+    <t>wind offshore electricity generation in cluster -- 12</t>
   </si>
   <si>
     <t>elc_wof_013</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 13</t>
+    <t>wind offshore electricity generation in cluster -- 13</t>
   </si>
   <si>
     <t>elc_wof_014</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 14</t>
+    <t>wind offshore electricity generation in cluster -- 14</t>
   </si>
   <si>
     <t>elc_wof_015</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 15</t>
+    <t>wind offshore electricity generation in cluster -- 15</t>
   </si>
   <si>
     <t>elc_wof_016</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 16</t>
+    <t>wind offshore electricity generation in cluster -- 16</t>
   </si>
   <si>
     <t>elc_wof_017</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 17</t>
+    <t>wind offshore electricity generation in cluster -- 17</t>
   </si>
   <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 18</t>
+    <t>wind offshore electricity generation in cluster -- 18</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 19</t>
+    <t>wind offshore electricity generation in cluster -- 19</t>
   </si>
   <si>
     <t>elc_wof_020</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 20</t>
+    <t>wind offshore electricity generation in cluster -- 20</t>
   </si>
   <si>
     <t>elc_wof_021</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 21</t>
+    <t>wind offshore electricity generation in cluster -- 21</t>
   </si>
   <si>
     <t>elc_wof_022</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 22</t>
+    <t>wind offshore electricity generation in cluster -- 22</t>
   </si>
   <si>
     <t>elc_wof_023</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 23</t>
+    <t>wind offshore electricity generation in cluster -- 23</t>
   </si>
   <si>
     <t>elc_wof_024</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 24</t>
+    <t>wind offshore electricity generation in cluster -- 24</t>
   </si>
   <si>
     <t>elc_wof_025</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 25</t>
+    <t>wind offshore electricity generation in cluster -- 25</t>
   </si>
   <si>
     <t>elc_wof_026</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 26</t>
+    <t>wind offshore electricity generation in cluster -- 26</t>
   </si>
   <si>
     <t>elc_wof_027</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 27</t>
+    <t>wind offshore electricity generation in cluster -- 27</t>
   </si>
   <si>
     <t>elc_wof_028</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 28</t>
+    <t>wind offshore electricity generation in cluster -- 28</t>
   </si>
   <si>
     <t>elc_wof_029</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 29</t>
+    <t>wind offshore electricity generation in cluster -- 29</t>
   </si>
   <si>
     <t>elc_wof_030</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 30</t>
+    <t>wind offshore electricity generation in cluster -- 30</t>
   </si>
   <si>
     <t>elc_wof_031</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 31</t>
+    <t>wind offshore electricity generation in cluster -- 31</t>
   </si>
   <si>
     <t>elc_wof_032</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 32</t>
+    <t>wind offshore electricity generation in cluster -- 32</t>
   </si>
   <si>
     <t>elc_wof_033</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 33</t>
+    <t>wind offshore electricity generation in cluster -- 33</t>
   </si>
   <si>
     <t>elc_wof_034</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 34</t>
+    <t>wind offshore electricity generation in cluster -- 34</t>
   </si>
   <si>
     <t>elc_wof_035</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 35</t>
+    <t>wind offshore electricity generation in cluster -- 35</t>
   </si>
   <si>
     <t>elc_wof_036</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 36</t>
+    <t>wind offshore electricity generation in cluster -- 36</t>
   </si>
   <si>
     <t>elc_wof_037</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 37</t>
+    <t>wind offshore electricity generation in cluster -- 37</t>
   </si>
   <si>
     <t>elc_wof_038</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 38</t>
+    <t>wind offshore electricity generation in cluster -- 38</t>
   </si>
   <si>
     <t>elc_wof_039</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 39</t>
+    <t>wind offshore electricity generation in cluster -- 39</t>
   </si>
   <si>
     <t>elc_wof_040</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 40</t>
+    <t>wind offshore electricity generation in cluster -- 40</t>
   </si>
   <si>
     <t>elc_wof_041</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 41</t>
+    <t>wind offshore electricity generation in cluster -- 41</t>
   </si>
   <si>
     <t>elc_wof_042</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 42</t>
+    <t>wind offshore electricity generation in cluster -- 42</t>
   </si>
   <si>
     <t>elc_wof_043</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 43</t>
+    <t>wind offshore electricity generation in cluster -- 43</t>
   </si>
   <si>
     <t>elc_wof_044</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 44</t>
+    <t>wind offshore electricity generation in cluster -- 44</t>
   </si>
   <si>
     <t>elc_wof_045</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 45</t>
+    <t>wind offshore electricity generation in cluster -- 45</t>
   </si>
   <si>
     <t>elc_wof_046</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 46</t>
+    <t>wind offshore electricity generation in cluster -- 46</t>
   </si>
   <si>
     <t>elc_wof_047</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 47</t>
+    <t>wind offshore electricity generation in cluster -- 47</t>
   </si>
   <si>
     <t>elc_wof_048</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 48</t>
+    <t>wind offshore electricity generation in cluster -- 48</t>
   </si>
   <si>
     <t>elc_wof_049</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 49</t>
+    <t>wind offshore electricity generation in cluster -- 49</t>
   </si>
   <si>
     <t>elc_wof_050</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 50</t>
+    <t>wind offshore electricity generation in cluster -- 50</t>
   </si>
   <si>
     <t>elc_wof_051</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 51</t>
+    <t>wind offshore electricity generation in cluster -- 51</t>
   </si>
   <si>
     <t>elc_wof_052</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 52</t>
+    <t>wind offshore electricity generation in cluster -- 52</t>
   </si>
   <si>
     <t>elc_wof_053</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 53</t>
+    <t>wind offshore electricity generation in cluster -- 53</t>
   </si>
   <si>
     <t>elc_wof_054</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 54</t>
+    <t>wind offshore electricity generation in cluster -- 54</t>
   </si>
   <si>
     <t>elc_wof_055</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 55</t>
+    <t>wind offshore electricity generation in cluster -- 55</t>
   </si>
   <si>
     <t>elc_wof_056</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 56</t>
+    <t>wind offshore electricity generation in cluster -- 56</t>
   </si>
   <si>
     <t>elc_wof_057</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 57</t>
+    <t>wind offshore electricity generation in cluster -- 57</t>
   </si>
   <si>
     <t>elc_wof_058</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 58</t>
+    <t>wind offshore electricity generation in cluster -- 58</t>
   </si>
   <si>
     <t>elc_wof_059</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 59</t>
+    <t>wind offshore electricity generation in cluster -- 59</t>
   </si>
   <si>
     <t>elc_wof_060</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 60</t>
+    <t>wind offshore electricity generation in cluster -- 60</t>
   </si>
   <si>
     <t>elc_wof_061</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 61</t>
+    <t>wind offshore electricity generation in cluster -- 61</t>
   </si>
   <si>
     <t>elc_wof_062</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 62</t>
+    <t>wind offshore electricity generation in cluster -- 62</t>
   </si>
   <si>
     <t>elc_wof_063</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 63</t>
+    <t>wind offshore electricity generation in cluster -- 63</t>
   </si>
   <si>
     <t>elc_wof_064</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 64</t>
+    <t>wind offshore electricity generation in cluster -- 64</t>
   </si>
   <si>
     <t>elc_wof_065</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 65</t>
+    <t>wind offshore electricity generation in cluster -- 65</t>
   </si>
   <si>
     <t>elc_wof_066</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 66</t>
+    <t>wind offshore electricity generation in cluster -- 66</t>
   </si>
   <si>
     <t>elc_wof_067</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 67</t>
+    <t>wind offshore electricity generation in cluster -- 67</t>
   </si>
   <si>
     <t>elc_wof_068</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 68</t>
+    <t>wind offshore electricity generation in cluster -- 68</t>
   </si>
   <si>
     <t>elc_wof_069</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 69</t>
+    <t>wind offshore electricity generation in cluster -- 69</t>
   </si>
   <si>
     <t>elc_wof_070</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 70</t>
+    <t>wind offshore electricity generation in cluster -- 70</t>
   </si>
   <si>
     <t>elc_wof_071</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 71</t>
+    <t>wind offshore electricity generation in cluster -- 71</t>
   </si>
   <si>
     <t>elc_wof_072</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 72</t>
+    <t>wind offshore electricity generation in cluster -- 72</t>
   </si>
   <si>
     <t>elc_wof_073</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 73</t>
+    <t>wind offshore electricity generation in cluster -- 73</t>
   </si>
   <si>
     <t>elc_wof_074</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 74</t>
+    <t>wind offshore electricity generation in cluster -- 74</t>
   </si>
   <si>
     <t>elc_wof_075</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 75</t>
+    <t>wind offshore electricity generation in cluster -- 75</t>
   </si>
   <si>
     <t>elc_wof_076</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 76</t>
+    <t>wind offshore electricity generation in cluster -- 76</t>
   </si>
   <si>
     <t>elc_wof_077</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 77</t>
+    <t>wind offshore electricity generation in cluster -- 77</t>
   </si>
   <si>
     <t>elc_wof_078</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 78</t>
+    <t>wind offshore electricity generation in cluster -- 78</t>
   </si>
   <si>
     <t>elc_wof_079</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 79</t>
+    <t>wind offshore electricity generation in cluster -- 79</t>
   </si>
   <si>
     <t>elc_wof_080</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 80</t>
+    <t>wind offshore electricity generation in cluster -- 80</t>
   </si>
   <si>
     <t>elc_wof_081</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 81</t>
+    <t>wind offshore electricity generation in cluster -- 81</t>
   </si>
   <si>
     <t>elc_wof_082</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 82</t>
+    <t>wind offshore electricity generation in cluster -- 82</t>
   </si>
   <si>
     <t>elc_wof_083</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 83</t>
+    <t>wind offshore electricity generation in cluster -- 83</t>
   </si>
   <si>
     <t>elc_wof_084</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 84</t>
+    <t>wind offshore electricity generation in cluster -- 84</t>
   </si>
   <si>
     <t>elc_wof_085</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 85</t>
+    <t>wind offshore electricity generation in cluster -- 85</t>
   </si>
   <si>
     <t>elc_wof_086</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 86</t>
+    <t>wind offshore electricity generation in cluster -- 86</t>
   </si>
   <si>
     <t>elc_wof_087</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 87</t>
+    <t>wind offshore electricity generation in cluster -- 87</t>
   </si>
   <si>
     <t>elc_wof_088</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 88</t>
+    <t>wind offshore electricity generation in cluster -- 88</t>
   </si>
   <si>
     <t>elc_wof_089</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 89</t>
+    <t>wind offshore electricity generation in cluster -- 89</t>
   </si>
   <si>
     <t>elc_wof_090</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 90</t>
+    <t>wind offshore electricity generation in cluster -- 90</t>
   </si>
   <si>
     <t>elc_wof_091</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 91</t>
+    <t>wind offshore electricity generation in cluster -- 91</t>
   </si>
   <si>
     <t>elc_wof_092</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 92</t>
+    <t>wind offshore electricity generation in cluster -- 92</t>
   </si>
   <si>
     <t>elc_wof_093</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 93</t>
+    <t>wind offshore electricity generation in cluster -- 93</t>
   </si>
   <si>
     <t>elc_wof_094</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 94</t>
+    <t>wind offshore electricity generation in cluster -- 94</t>
   </si>
   <si>
     <t>elc_wof_095</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 95</t>
+    <t>wind offshore electricity generation in cluster -- 95</t>
   </si>
   <si>
     <t>elc_wof_096</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 96</t>
+    <t>wind offshore electricity generation in cluster -- 96</t>
   </si>
   <si>
     <t>elc_wof_097</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 97</t>
+    <t>wind offshore electricity generation in cluster -- 97</t>
   </si>
   <si>
     <t>elc_wof_098</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 98</t>
+    <t>wind offshore electricity generation in cluster -- 98</t>
   </si>
   <si>
     <t>elc_wof_099</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 99</t>
+    <t>wind offshore electricity generation in cluster -- 99</t>
   </si>
   <si>
     <t>elc_wof_100</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 100</t>
+    <t>wind offshore electricity generation in cluster -- 100</t>
   </si>
   <si>
     <t>elc_wof_101</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 101</t>
+    <t>wind offshore electricity generation in cluster -- 101</t>
   </si>
   <si>
     <t>elc_wof_102</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 102</t>
+    <t>wind offshore electricity generation in cluster -- 102</t>
   </si>
   <si>
     <t>elc_wof_103</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 103</t>
+    <t>wind offshore electricity generation in cluster -- 103</t>
   </si>
   <si>
     <t>elc_wof_104</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 104</t>
+    <t>wind offshore electricity generation in cluster -- 104</t>
   </si>
   <si>
     <t>elc_wof_105</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 105</t>
+    <t>wind offshore electricity generation in cluster -- 105</t>
   </si>
   <si>
     <t>elc_wof_106</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 106</t>
+    <t>wind offshore electricity generation in cluster -- 106</t>
   </si>
   <si>
     <t>elc_wof_107</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 107</t>
+    <t>wind offshore electricity generation in cluster -- 107</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EA17680-B65B-4E39-A80A-2A35C881B29F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00C9225-20E3-4E49-BDB8-C32F5F8BF74B}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AFA849-8C0D-4F01-BECC-A65CDF901227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AC93C1-FD40-43CC-BDA3-C8290464B3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00C9225-20E3-4E49-BDB8-C32F5F8BF74B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD78125-1668-443A-AE09-F05BC2D48E5E}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AC93C1-FD40-43CC-BDA3-C8290464B3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA2ACB7-DD91-4D6F-B816-01E3CC7AA797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD78125-1668-443A-AE09-F05BC2D48E5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264ACC09-9327-4622-85D7-3049E2DCDE95}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA2ACB7-DD91-4D6F-B816-01E3CC7AA797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255933F0-3954-4E4D-A138-6BFAB9108C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264ACC09-9327-4622-85D7-3049E2DCDE95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9496232-9396-4969-AC9A-149CA663D104}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255933F0-3954-4E4D-A138-6BFAB9108C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922CBC60-F7CE-4D8D-9239-1C56B005922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9496232-9396-4969-AC9A-149CA663D104}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B404BE9-37D3-43C3-AA0B-050C8B0314CF}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SysSettings.xlsx
+++ b/VerveStacks_CAN_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922CBC60-F7CE-4D8D-9239-1C56B005922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B91734-B6D8-426D-A0BE-D63CD09F7350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8042,7 +8042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B404BE9-37D3-43C3-AA0B-050C8B0314CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76ECEFF-C15E-4769-8EE9-C383ABA2AD6D}">
   <dimension ref="B3:H496"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
